--- a/260910_휴머노이드 작업 플로우 소요시간(chassis_sequence 기준)_v0.1.xlsx
+++ b/260910_휴머노이드 작업 플로우 소요시간(chassis_sequence 기준)_v0.1.xlsx
@@ -2,7 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
